--- a/Items.xlsx
+++ b/Items.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\3D Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA87066-B71F-4747-BCB8-E2224880305F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C86F839-7C71-4FA3-8E55-2DA8870D9DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>ID</t>
   </si>
@@ -33,9 +44,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Battery</t>
-  </si>
-  <si>
     <t>Card</t>
   </si>
   <si>
@@ -61,6 +69,30 @@
   </si>
   <si>
     <t>Big Battery</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Battery AA</t>
+  </si>
+  <si>
+    <t>Battery C</t>
+  </si>
+  <si>
+    <t>Cable</t>
+  </si>
+  <si>
+    <t>Yellow Gem</t>
+  </si>
+  <si>
+    <t>Green Gem</t>
+  </si>
+  <si>
+    <t>USB Key</t>
+  </si>
+  <si>
+    <t>Lighter</t>
   </si>
 </sst>
 </file>
@@ -378,14 +410,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B151"/>
+  <dimension ref="A1:C151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.44140625" customWidth="1"/>
     <col min="2" max="2" width="24.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -393,98 +425,119 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -914,7 +967,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
@@ -922,7 +975,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
@@ -930,7 +983,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">

--- a/Items.xlsx
+++ b/Items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\3D Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C86F839-7C71-4FA3-8E55-2DA8870D9DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F818D38D-6C31-4483-942B-501F29B042B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>ID</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>Lighter</t>
+  </si>
+  <si>
+    <t>Blue Gem</t>
   </si>
 </sst>
 </file>
@@ -536,6 +539,9 @@
       <c r="A15">
         <v>14</v>
       </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">

--- a/Items.xlsx
+++ b/Items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\3D Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14EF6AE4-DBF0-49AD-B4E9-C02C6671EB28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD86E1C-53F3-4C86-8247-0BBE85C47204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t>ID</t>
   </si>
@@ -95,18 +95,6 @@
     <t>Blue Gem</t>
   </si>
   <si>
-    <t>Cabinet 1</t>
-  </si>
-  <si>
-    <t>Cabinet</t>
-  </si>
-  <si>
-    <t>Cabinet 2</t>
-  </si>
-  <si>
-    <t>Cabinet 3</t>
-  </si>
-  <si>
     <t>Required</t>
   </si>
   <si>
@@ -114,25 +102,13 @@
   </si>
   <si>
     <t>Status</t>
-  </si>
-  <si>
-    <t>Cabinet 4</t>
-  </si>
-  <si>
-    <t>Cabinet 5</t>
-  </si>
-  <si>
-    <t>Cabinet 6</t>
-  </si>
-  <si>
-    <t>Cabinet 7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,6 +155,11 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -189,7 +170,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -206,19 +187,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,1142 +479,1325 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P151"/>
+  <dimension ref="A1:X151"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="1"/>
-    <col min="4" max="4" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.21875" style="11" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="1"/>
-    <col min="9" max="9" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="4.44140625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="4"/>
+    <col min="4" max="4" width="14.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="24" width="3.77734375" style="4" customWidth="1"/>
+    <col min="25" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I1" s="7" t="s">
+      <c r="F1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="7" t="s">
+      <c r="H1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="I1" s="1">
+        <v>0</v>
+      </c>
+      <c r="J1" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1" s="1">
+        <v>3</v>
+      </c>
+      <c r="M1" s="1">
+        <v>4</v>
+      </c>
+      <c r="N1" s="1">
+        <v>5</v>
+      </c>
+      <c r="O1" s="1">
+        <v>6</v>
+      </c>
+      <c r="P1" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>8</v>
+      </c>
+      <c r="R1" s="1">
+        <v>9</v>
+      </c>
+      <c r="S1" s="1">
+        <v>10</v>
+      </c>
+      <c r="T1" s="1">
         <v>11</v>
       </c>
-      <c r="C2" s="3">
+      <c r="U1" s="1">
+        <v>12</v>
+      </c>
+      <c r="V1" s="1">
+        <v>13</v>
+      </c>
+      <c r="W1" s="1">
+        <v>14</v>
+      </c>
+      <c r="X1" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="4">
         <v>10</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="4">
         <v>12</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="5">
         <f>SUM(C2:E2)</f>
         <v>22</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="6">
         <f>SUM(I2:Z2)</f>
-        <v>7</v>
-      </c>
-      <c r="H2" s="3" t="str">
+        <v>24</v>
+      </c>
+      <c r="H2" s="4" t="str">
         <f>IF(G2&gt;=F2, "OK", "")</f>
-        <v/>
-      </c>
-      <c r="L2" s="3">
-        <v>3</v>
-      </c>
-      <c r="O2" s="3">
+        <v>OK</v>
+      </c>
+      <c r="I2" s="4">
+        <v>2</v>
+      </c>
+      <c r="L2" s="4">
+        <v>3</v>
+      </c>
+      <c r="O2" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="R2" s="4">
+        <v>2</v>
+      </c>
+      <c r="S2" s="4">
+        <v>4</v>
+      </c>
+      <c r="U2" s="4">
+        <v>4</v>
+      </c>
+      <c r="V2" s="4">
+        <v>3</v>
+      </c>
+      <c r="W2" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="5">
         <f t="shared" ref="F3:F14" si="0">SUM(C3:E3)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="6">
         <f t="shared" ref="G3:G15" si="1">SUM(I3:Z3)</f>
-        <v>1</v>
-      </c>
-      <c r="H3" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="H3" s="4" t="str">
         <f t="shared" ref="H3:H15" si="2">IF(G3&gt;=F3, "OK", "")</f>
         <v>OK</v>
       </c>
-      <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3">
-        <v>2</v>
-      </c>
-      <c r="F4" s="4">
+      <c r="M3" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="8">
+        <v>2</v>
+      </c>
+      <c r="F4" s="9">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="G4" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="H4" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="H4" s="8" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O4" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
+        <v>OK</v>
+      </c>
+      <c r="J4" s="8">
+        <v>1</v>
+      </c>
+      <c r="O4" s="8">
+        <v>1</v>
+      </c>
+      <c r="T4" s="8">
+        <v>1</v>
+      </c>
+      <c r="U4" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="6">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="H5" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="H5" s="4" t="str">
         <f t="shared" si="2"/>
         <v>OK</v>
       </c>
-      <c r="O5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+      <c r="O5" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="4">
         <v>6</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="4">
         <v>6</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="6">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="H6" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>OK</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1</v>
+      </c>
+      <c r="K6" s="4">
+        <v>1</v>
+      </c>
+      <c r="N6" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>2</v>
+      </c>
+      <c r="R6" s="4">
+        <v>3</v>
+      </c>
+      <c r="T6" s="4">
+        <v>2</v>
+      </c>
+      <c r="U6" s="4">
+        <v>2</v>
+      </c>
+      <c r="W6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4">
+        <v>12</v>
+      </c>
+      <c r="F7" s="5">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="G7" s="6">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="H7" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>OK</v>
+      </c>
+      <c r="I7" s="4">
+        <v>3</v>
+      </c>
+      <c r="L7" s="4">
+        <v>2</v>
+      </c>
+      <c r="R7" s="4">
+        <v>1</v>
+      </c>
+      <c r="S7" s="4">
+        <v>2</v>
+      </c>
+      <c r="T7" s="4">
+        <v>2</v>
+      </c>
+      <c r="V7" s="4">
+        <v>3</v>
+      </c>
+      <c r="X7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="4">
+        <v>3</v>
+      </c>
+      <c r="F8" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G8" s="6">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="H8" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>OK</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1</v>
+      </c>
+      <c r="S8" s="4">
+        <v>1</v>
+      </c>
+      <c r="U8" s="4">
+        <v>1</v>
+      </c>
+      <c r="V8" s="4">
+        <v>1</v>
+      </c>
+      <c r="W8" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="4">
+        <v>8</v>
+      </c>
+      <c r="E9" s="4">
+        <v>8</v>
+      </c>
+      <c r="F9" s="5">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="G9" s="6">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="H9" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>OK</v>
+      </c>
+      <c r="I9" s="4">
+        <v>2</v>
+      </c>
+      <c r="J9" s="4">
+        <v>2</v>
+      </c>
+      <c r="L9" s="4">
+        <v>1</v>
+      </c>
+      <c r="P9" s="4">
+        <v>2</v>
+      </c>
+      <c r="R9" s="4">
+        <v>2</v>
+      </c>
+      <c r="T9" s="4">
+        <v>2</v>
+      </c>
+      <c r="V9" s="4">
+        <v>2</v>
+      </c>
+      <c r="W9" s="4">
+        <v>2</v>
+      </c>
+      <c r="X9" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="4">
+        <v>4</v>
+      </c>
+      <c r="E10" s="4">
+        <v>3</v>
+      </c>
+      <c r="F10" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="G10" s="6">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="H10" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>OK</v>
+      </c>
+      <c r="J10" s="4">
+        <v>1</v>
+      </c>
+      <c r="M10" s="4">
+        <v>1</v>
+      </c>
+      <c r="N10" s="4">
+        <v>1</v>
+      </c>
+      <c r="S10" s="4">
+        <v>2</v>
+      </c>
+      <c r="V10" s="4">
+        <v>1</v>
+      </c>
+      <c r="W10" s="4">
+        <v>1</v>
+      </c>
+      <c r="X10" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="4">
+        <v>14</v>
+      </c>
+      <c r="F11" s="5">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="G11" s="6">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="H11" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>OK</v>
+      </c>
+      <c r="K11" s="4">
+        <v>2</v>
+      </c>
+      <c r="M11" s="4">
+        <v>4</v>
+      </c>
+      <c r="P11" s="4">
+        <v>3</v>
+      </c>
+      <c r="R11" s="4">
+        <v>2</v>
+      </c>
+      <c r="T11" s="4">
+        <v>1</v>
+      </c>
+      <c r="V11" s="4">
+        <v>2</v>
+      </c>
+      <c r="X11" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="4">
+        <v>15</v>
+      </c>
+      <c r="F12" s="5">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="G12" s="6">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="H12" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>OK</v>
+      </c>
+      <c r="I12" s="4">
+        <v>2</v>
+      </c>
+      <c r="K12" s="7">
+        <v>3</v>
+      </c>
+      <c r="N12" s="4">
+        <v>3</v>
+      </c>
+      <c r="O12" s="4">
+        <v>2</v>
+      </c>
+      <c r="P12" s="4">
+        <v>4</v>
+      </c>
+      <c r="T12" s="4">
+        <v>1</v>
+      </c>
+      <c r="X12" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="4">
+        <v>2</v>
+      </c>
+      <c r="F13" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G13" s="6">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="H6" s="3" t="str">
+      <c r="H13" s="4" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="I6" s="3">
-        <v>1</v>
-      </c>
-      <c r="K6" s="3">
-        <v>1</v>
-      </c>
-      <c r="N6" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3">
-        <v>12</v>
-      </c>
-      <c r="F7" s="4">
+        <v>OK</v>
+      </c>
+      <c r="L13" s="4">
+        <v>1</v>
+      </c>
+      <c r="M13" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="4">
+        <v>3</v>
+      </c>
+      <c r="F14" s="5">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="G7" s="10">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="H7" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="I7" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="3">
-        <v>3</v>
-      </c>
-      <c r="F8" s="4">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G8" s="10">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="H8" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="3">
-        <v>8</v>
-      </c>
-      <c r="E9" s="3">
-        <v>8</v>
-      </c>
-      <c r="F9" s="4">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="G9" s="10">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="H9" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="I9" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="3">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3">
-        <v>3</v>
-      </c>
-      <c r="F10" s="4">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="G10" s="10">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="H10" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="M10" s="3">
-        <v>1</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="3">
-        <v>14</v>
-      </c>
-      <c r="F11" s="4">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="G11" s="10">
+        <v>3</v>
+      </c>
+      <c r="G14" s="6">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="H11" s="3" t="str">
+      <c r="H14" s="4" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K11" s="3">
-        <v>2</v>
-      </c>
-      <c r="P11" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="3">
-        <v>15</v>
-      </c>
-      <c r="F12" s="4">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="G12" s="10">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="H12" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P12" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="3">
-        <v>2</v>
-      </c>
-      <c r="F13" s="4">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G13" s="10">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="H13" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="M13" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="3">
-        <v>3</v>
-      </c>
-      <c r="F14" s="4">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G14" s="10">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="H14" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P14" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5">
+        <v>OK</v>
+      </c>
+      <c r="L14" s="4">
+        <v>1</v>
+      </c>
+      <c r="P14" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="5">
         <f>SUM(C15:E15)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="6">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="H15" s="3" t="str">
+      <c r="H15" s="4" t="str">
         <f t="shared" si="2"/>
         <v>OK</v>
       </c>
-      <c r="J15" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
+      <c r="J15" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
+      <c r="A18" s="4">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
+      <c r="A20" s="4">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
+      <c r="A21" s="4">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
+      <c r="A22" s="4">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
+      <c r="A23" s="4">
         <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
+      <c r="A24" s="4">
         <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
+      <c r="A25" s="4">
         <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+      <c r="A26" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
+      <c r="A27" s="4">
         <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
+      <c r="A28" s="4">
         <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
+      <c r="A29" s="4">
         <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
+      <c r="A30" s="4">
         <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
+      <c r="A31" s="4">
         <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
+      <c r="A32" s="4">
         <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
+      <c r="A33" s="4">
         <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+      <c r="A34" s="4">
         <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
+      <c r="A35" s="4">
         <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
+      <c r="A36" s="4">
         <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
+      <c r="A37" s="4">
         <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
+      <c r="A38" s="4">
         <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
+      <c r="A39" s="4">
         <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
+      <c r="A40" s="4">
         <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
+      <c r="A41" s="4">
         <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
+      <c r="A42" s="4">
         <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
+      <c r="A43" s="4">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
+      <c r="A44" s="4">
         <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
+      <c r="A45" s="4">
         <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
+      <c r="A46" s="4">
         <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="1">
+      <c r="A47" s="4">
         <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
+      <c r="A48" s="4">
         <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
+      <c r="A49" s="4">
         <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
+      <c r="A50" s="4">
         <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="1">
+      <c r="A51" s="4">
         <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
+      <c r="A52" s="4">
         <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
+      <c r="A53" s="4">
         <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
+      <c r="A54" s="4">
         <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="1">
+      <c r="A55" s="4">
         <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="1">
+      <c r="A56" s="4">
         <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="1">
+      <c r="A57" s="4">
         <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="1">
+      <c r="A58" s="4">
         <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="1">
+      <c r="A59" s="4">
         <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="1">
+      <c r="A60" s="4">
         <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="1">
+      <c r="A61" s="4">
         <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="1">
+      <c r="A62" s="4">
         <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="1">
+      <c r="A63" s="4">
         <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="1">
+      <c r="A64" s="4">
         <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="1">
+      <c r="A65" s="4">
         <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="1">
+      <c r="A66" s="4">
         <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="1">
+      <c r="A67" s="4">
         <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="1">
+      <c r="A68" s="4">
         <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="1">
+      <c r="A69" s="4">
         <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="1">
+      <c r="A70" s="4">
         <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="1">
+      <c r="A71" s="4">
         <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="1">
+      <c r="A72" s="4">
         <v>71</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="1">
+      <c r="A73" s="4">
         <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="1">
+      <c r="A74" s="4">
         <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="1">
+      <c r="A75" s="4">
         <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="1">
+      <c r="A76" s="4">
         <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="1">
+      <c r="A77" s="4">
         <v>76</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="1">
+      <c r="A78" s="4">
         <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="1">
+      <c r="A79" s="4">
         <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="1">
+      <c r="A80" s="4">
         <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="1">
+      <c r="A81" s="4">
         <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="1">
+      <c r="A82" s="4">
         <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="1">
+      <c r="A83" s="4">
         <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="1">
+      <c r="A84" s="4">
         <v>83</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="1">
+      <c r="A85" s="4">
         <v>84</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="1">
+      <c r="A86" s="4">
         <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="1">
+      <c r="A87" s="4">
         <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" s="1">
+      <c r="A88" s="4">
         <v>87</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" s="1">
+      <c r="A89" s="4">
         <v>88</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="1">
+      <c r="A90" s="4">
         <v>89</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="1">
+      <c r="A91" s="4">
         <v>90</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" s="1">
+      <c r="A92" s="4">
         <v>91</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" s="1">
+      <c r="A93" s="4">
         <v>92</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" s="1">
+      <c r="A94" s="4">
         <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" s="1">
+      <c r="A95" s="4">
         <v>94</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="1">
+      <c r="A96" s="4">
         <v>95</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97" s="1">
+      <c r="A97" s="4">
         <v>96</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A98" s="1">
+      <c r="A98" s="4">
         <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A99" s="1">
+      <c r="A99" s="4">
         <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A100" s="1">
+      <c r="A100" s="4">
         <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101" s="1">
+      <c r="A101" s="4">
         <v>100</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B101" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A102" s="1">
+      <c r="A102" s="4">
         <v>101</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B102" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A103" s="1">
+      <c r="A103" s="4">
         <v>102</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B103" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A104" s="1">
+      <c r="A104" s="4">
         <v>103</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A105" s="1">
+      <c r="A105" s="4">
         <v>104</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A106" s="1">
+      <c r="A106" s="4">
         <v>105</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A107" s="1">
+      <c r="A107" s="4">
         <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A108" s="1">
+      <c r="A108" s="4">
         <v>107</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A109" s="1">
+      <c r="A109" s="4">
         <v>108</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A110" s="1">
+      <c r="A110" s="4">
         <v>109</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A111" s="1">
+      <c r="A111" s="4">
         <v>110</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A112" s="1">
+      <c r="A112" s="4">
         <v>111</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" s="1">
+      <c r="A113" s="4">
         <v>112</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A114" s="1">
+      <c r="A114" s="4">
         <v>113</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A115" s="1">
+      <c r="A115" s="4">
         <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A116" s="1">
+      <c r="A116" s="4">
         <v>115</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A117" s="1">
+      <c r="A117" s="4">
         <v>116</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A118" s="1">
+      <c r="A118" s="4">
         <v>117</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A119" s="1">
+      <c r="A119" s="4">
         <v>118</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A120" s="1">
+      <c r="A120" s="4">
         <v>119</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A121" s="1">
+      <c r="A121" s="4">
         <v>120</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" s="1">
+      <c r="A122" s="4">
         <v>121</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" s="1">
+      <c r="A123" s="4">
         <v>122</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A124" s="1">
+      <c r="A124" s="4">
         <v>123</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A125" s="1">
+      <c r="A125" s="4">
         <v>124</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" s="1">
+      <c r="A126" s="4">
         <v>125</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A127" s="1">
+      <c r="A127" s="4">
         <v>126</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A128" s="1">
+      <c r="A128" s="4">
         <v>127</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A129" s="1">
+      <c r="A129" s="4">
         <v>128</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A130" s="1">
+      <c r="A130" s="4">
         <v>129</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" s="1">
+      <c r="A131" s="4">
         <v>130</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A132" s="1">
+      <c r="A132" s="4">
         <v>131</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A133" s="1">
+      <c r="A133" s="4">
         <v>132</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A134" s="1">
+      <c r="A134" s="4">
         <v>133</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A135" s="1">
+      <c r="A135" s="4">
         <v>134</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A136" s="1">
+      <c r="A136" s="4">
         <v>135</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A137" s="1">
+      <c r="A137" s="4">
         <v>136</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A138" s="1">
+      <c r="A138" s="4">
         <v>137</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A139" s="1">
+      <c r="A139" s="4">
         <v>138</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A140" s="1">
+      <c r="A140" s="4">
         <v>139</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A141" s="1">
+      <c r="A141" s="4">
         <v>140</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A142" s="1">
+      <c r="A142" s="4">
         <v>141</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A143" s="1">
+      <c r="A143" s="4">
         <v>142</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A144" s="1">
+      <c r="A144" s="4">
         <v>143</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A145" s="1">
+      <c r="A145" s="4">
         <v>144</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A146" s="1">
+      <c r="A146" s="4">
         <v>145</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A147" s="1">
+      <c r="A147" s="4">
         <v>146</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A148" s="1">
+      <c r="A148" s="4">
         <v>147</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A149" s="1">
+      <c r="A149" s="4">
         <v>148</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A150" s="1">
+      <c r="A150" s="4">
         <v>149</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A151" s="1">
+      <c r="A151" s="4">
         <v>150</v>
       </c>
     </row>

--- a/Items.xlsx
+++ b/Items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\3D Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD86E1C-53F3-4C86-8247-0BBE85C47204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480106FE-4173-4D8E-A3D3-E98B9F9C82D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>ID</t>
   </si>
@@ -102,6 +102,57 @@
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
   </si>
 </sst>
 </file>
@@ -161,18 +212,12 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -189,21 +234,508 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="7" tint="-0.499984740745262"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -214,6 +746,46 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4A650520-C7D5-4FFF-8EC3-CE69901F8B25}" name="Table4" displayName="Table4" ref="A1:Y14" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A1:Y14" xr:uid="{4A650520-C7D5-4FFF-8EC3-CE69901F8B25}"/>
+  <tableColumns count="25">
+    <tableColumn id="1" xr3:uid="{D2EA52A8-D120-451A-8C3A-8285FCF2B5F7}" name="ID" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{08549C34-9BBD-4E28-AA25-2BD2215C4076}" name="Name" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{49ACF0F6-2D9D-468B-A66D-79335A820BE7}" name="Engine" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{CA452EBF-293F-4EA4-A651-EBF51F92EE8D}" name="Wiring System" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{0CAAF9F6-97B3-4424-9AFA-223FD0F1544B}" name="Big Battery" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{80CC1A83-6F82-4E55-ACB5-2BFAB99389BD}" name="Required" dataDxfId="21">
+      <calculatedColumnFormula>SUM(C2:E2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{8160937C-AA10-4B66-980B-811886276B93}" name="Available" dataDxfId="20">
+      <calculatedColumnFormula>SUM(I2:Z2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{E0FEA25D-A3FA-48D7-B0D8-893880F67930}" name="Status" dataDxfId="19">
+      <calculatedColumnFormula>IF(G2&gt;=F2, "OK", "")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{E07AB1DB-5D76-4D4A-ABBD-E5E9E50EB8C7}" name="0" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{81717C64-19AE-4844-B7F9-777899752382}" name="1" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{F74E9D07-6EA1-47BA-859A-8EC6358D2293}" name="2" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{072BA86D-F274-4183-96F9-728CC82922D9}" name="3" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{E36BC491-A68B-4595-9F73-4EC8782C8890}" name="4" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{84AC78DB-F38E-4A09-B16E-6FC73C7385D6}" name="5" dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{AE2255F0-55BB-4EBA-B555-53C08E0AD340}" name="6" dataDxfId="12"/>
+    <tableColumn id="16" xr3:uid="{DC10F21C-EEC5-451A-8133-6C400CEFA48A}" name="7" dataDxfId="11"/>
+    <tableColumn id="17" xr3:uid="{5B0E20C0-A965-47E7-B220-2FC3781808A2}" name="8" dataDxfId="10"/>
+    <tableColumn id="18" xr3:uid="{9012B878-29D5-429E-AE2F-702FE0B7E4ED}" name="9" dataDxfId="9"/>
+    <tableColumn id="19" xr3:uid="{795A1C20-3F30-4D31-B2C1-616178E686C5}" name="10" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{BD14ACEA-4C27-407B-9F44-4441FAE0A695}" name="11" dataDxfId="7"/>
+    <tableColumn id="21" xr3:uid="{559389C0-BFC6-48DE-827C-5706F746A67F}" name="12" dataDxfId="6"/>
+    <tableColumn id="22" xr3:uid="{22B66430-28FB-4EFF-86DA-E6FEF13427A1}" name="13" dataDxfId="5"/>
+    <tableColumn id="23" xr3:uid="{FD7803DF-E65A-4D87-A1DA-FDAA6B392D2B}" name="14" dataDxfId="4"/>
+    <tableColumn id="24" xr3:uid="{41BBF050-A9B4-49FF-A7B3-AF5D66D03162}" name="15" dataDxfId="3"/>
+    <tableColumn id="25" xr3:uid="{B2BFE9A6-F6A1-4867-B0FA-CC30A76A7754}" name="16" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -479,22 +1051,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X151"/>
+  <dimension ref="A1:Y151"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.44140625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="5.21875" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.33203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="4"/>
-    <col min="4" max="4" width="14.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="24" width="3.77734375" style="4" customWidth="1"/>
-    <col min="25" max="16384" width="8.88671875" style="4"/>
+    <col min="3" max="3" width="9.33203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="8.77734375" style="4" customWidth="1"/>
+    <col min="9" max="18" width="4" style="4" customWidth="1"/>
+    <col min="19" max="25" width="5.109375" style="4" customWidth="1"/>
+    <col min="26" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -519,56 +1092,59 @@
       <c r="H1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="1">
-        <v>0</v>
-      </c>
-      <c r="J1" s="1">
-        <v>1</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1" s="1">
-        <v>3</v>
-      </c>
-      <c r="M1" s="1">
-        <v>4</v>
-      </c>
-      <c r="N1" s="1">
-        <v>5</v>
-      </c>
-      <c r="O1" s="1">
-        <v>6</v>
-      </c>
-      <c r="P1" s="1">
-        <v>7</v>
-      </c>
-      <c r="Q1" s="1">
-        <v>8</v>
-      </c>
-      <c r="R1" s="1">
-        <v>9</v>
-      </c>
-      <c r="S1" s="1">
-        <v>10</v>
-      </c>
-      <c r="T1" s="1">
-        <v>11</v>
-      </c>
-      <c r="U1" s="1">
-        <v>12</v>
-      </c>
-      <c r="V1" s="1">
-        <v>13</v>
-      </c>
-      <c r="W1" s="1">
-        <v>14</v>
-      </c>
-      <c r="X1" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="I1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -612,13 +1188,16 @@
         <v>4</v>
       </c>
       <c r="V2" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W2" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Y2" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -630,11 +1209,11 @@
         <v>0</v>
       </c>
       <c r="G3" s="6">
-        <f t="shared" ref="G3:G15" si="1">SUM(I3:Z3)</f>
+        <f>SUM(I3:Z3)</f>
         <v>3</v>
       </c>
       <c r="H3" s="4" t="str">
-        <f t="shared" ref="H3:H15" si="2">IF(G3&gt;=F3, "OK", "")</f>
+        <f t="shared" ref="H3:H15" si="1">IF(G3&gt;=F3, "OK", "")</f>
         <v>OK</v>
       </c>
       <c r="M3" s="4">
@@ -644,7 +1223,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -659,11 +1238,11 @@
         <v>2</v>
       </c>
       <c r="G4" s="10">
+        <f>SUM(I4:Z4)</f>
+        <v>4</v>
+      </c>
+      <c r="H4" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="H4" s="8" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="J4" s="8">
@@ -679,7 +1258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -691,11 +1270,11 @@
         <v>0</v>
       </c>
       <c r="G5" s="6">
+        <f>SUM(I5:Z5)</f>
+        <v>3</v>
+      </c>
+      <c r="H5" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="H5" s="4" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="O5" s="4">
@@ -705,7 +1284,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -723,11 +1302,11 @@
         <v>12</v>
       </c>
       <c r="G6" s="6">
+        <f>SUM(I6:Z6)</f>
+        <v>14</v>
+      </c>
+      <c r="H6" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="H6" s="4" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="I6" s="4">
@@ -755,7 +1334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -770,11 +1349,11 @@
         <v>12</v>
       </c>
       <c r="G7" s="6">
+        <f>SUM(I7:Z7)</f>
+        <v>14</v>
+      </c>
+      <c r="H7" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="H7" s="4" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="I7" s="4">
@@ -799,7 +1378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -814,11 +1393,11 @@
         <v>3</v>
       </c>
       <c r="G8" s="6">
+        <f>SUM(I8:Z8)</f>
+        <v>5</v>
+      </c>
+      <c r="H8" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="H8" s="4" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="J8" s="4">
@@ -837,7 +1416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -855,11 +1434,11 @@
         <v>16</v>
       </c>
       <c r="G9" s="6">
+        <f>SUM(I9:Z9)</f>
+        <v>18</v>
+      </c>
+      <c r="H9" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="H9" s="4" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="I9" s="4">
@@ -878,9 +1457,6 @@
         <v>2</v>
       </c>
       <c r="T9" s="4">
-        <v>2</v>
-      </c>
-      <c r="V9" s="4">
         <v>2</v>
       </c>
       <c r="W9" s="4">
@@ -889,8 +1465,11 @@
       <c r="X9" s="4">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y9" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -908,11 +1487,11 @@
         <v>7</v>
       </c>
       <c r="G10" s="6">
+        <f>SUM(I10:Z10)</f>
+        <v>9</v>
+      </c>
+      <c r="H10" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="H10" s="4" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="J10" s="4">
@@ -937,7 +1516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -952,11 +1531,11 @@
         <v>14</v>
       </c>
       <c r="G11" s="6">
+        <f>SUM(I11:Z11)</f>
+        <v>16</v>
+      </c>
+      <c r="H11" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="H11" s="4" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="K11" s="4">
@@ -981,7 +1560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -996,11 +1575,11 @@
         <v>15</v>
       </c>
       <c r="G12" s="6">
+        <f>SUM(I12:Z12)</f>
+        <v>17</v>
+      </c>
+      <c r="H12" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="H12" s="4" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="I12" s="4">
@@ -1021,11 +1600,11 @@
       <c r="T12" s="4">
         <v>1</v>
       </c>
-      <c r="X12" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y12" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -1040,11 +1619,11 @@
         <v>2</v>
       </c>
       <c r="G13" s="6">
+        <f>SUM(I13:Z13)</f>
+        <v>4</v>
+      </c>
+      <c r="H13" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="H13" s="4" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="L13" s="4">
@@ -1057,7 +1636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -1072,11 +1651,11 @@
         <v>3</v>
       </c>
       <c r="G14" s="6">
+        <f>SUM(I14:Z14)</f>
+        <v>5</v>
+      </c>
+      <c r="H14" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="H14" s="4" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="L14" s="4">
@@ -1089,7 +1668,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -1101,18 +1680,18 @@
         <v>0</v>
       </c>
       <c r="G15" s="6">
+        <f>SUM(I15:Z15)</f>
+        <v>2</v>
+      </c>
+      <c r="H15" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="H15" s="4" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="J15" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -1803,5 +2382,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Items.xlsx
+++ b/Items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\3D Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480106FE-4173-4D8E-A3D3-E98B9F9C82D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C94A25-1802-42E1-87D1-FAEACF0984B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -212,12 +212,18 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -241,9 +247,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -251,475 +257,475 @@
   <dxfs count="27">
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="7" tint="-0.499984740745262"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="7" tint="-0.499984740745262"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -749,40 +755,40 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4A650520-C7D5-4FFF-8EC3-CE69901F8B25}" name="Table4" displayName="Table4" ref="A1:Y14" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4A650520-C7D5-4FFF-8EC3-CE69901F8B25}" name="Table4" displayName="Table4" ref="A1:Y14" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="A1:Y14" xr:uid="{4A650520-C7D5-4FFF-8EC3-CE69901F8B25}"/>
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D2EA52A8-D120-451A-8C3A-8285FCF2B5F7}" name="ID" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{08549C34-9BBD-4E28-AA25-2BD2215C4076}" name="Name" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{49ACF0F6-2D9D-468B-A66D-79335A820BE7}" name="Engine" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{CA452EBF-293F-4EA4-A651-EBF51F92EE8D}" name="Wiring System" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{0CAAF9F6-97B3-4424-9AFA-223FD0F1544B}" name="Big Battery" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{80CC1A83-6F82-4E55-ACB5-2BFAB99389BD}" name="Required" dataDxfId="21">
+    <tableColumn id="1" xr3:uid="{D2EA52A8-D120-451A-8C3A-8285FCF2B5F7}" name="ID" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{08549C34-9BBD-4E28-AA25-2BD2215C4076}" name="Name" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{49ACF0F6-2D9D-468B-A66D-79335A820BE7}" name="Engine" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{CA452EBF-293F-4EA4-A651-EBF51F92EE8D}" name="Wiring System" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{0CAAF9F6-97B3-4424-9AFA-223FD0F1544B}" name="Big Battery" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{80CC1A83-6F82-4E55-ACB5-2BFAB99389BD}" name="Required" dataDxfId="19">
       <calculatedColumnFormula>SUM(C2:E2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8160937C-AA10-4B66-980B-811886276B93}" name="Available" dataDxfId="20">
+    <tableColumn id="7" xr3:uid="{8160937C-AA10-4B66-980B-811886276B93}" name="Available" dataDxfId="18">
       <calculatedColumnFormula>SUM(I2:Z2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{E0FEA25D-A3FA-48D7-B0D8-893880F67930}" name="Status" dataDxfId="19">
+    <tableColumn id="8" xr3:uid="{E0FEA25D-A3FA-48D7-B0D8-893880F67930}" name="Status" dataDxfId="17">
       <calculatedColumnFormula>IF(G2&gt;=F2, "OK", "")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E07AB1DB-5D76-4D4A-ABBD-E5E9E50EB8C7}" name="0" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{81717C64-19AE-4844-B7F9-777899752382}" name="1" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{F74E9D07-6EA1-47BA-859A-8EC6358D2293}" name="2" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{072BA86D-F274-4183-96F9-728CC82922D9}" name="3" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{E36BC491-A68B-4595-9F73-4EC8782C8890}" name="4" dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{84AC78DB-F38E-4A09-B16E-6FC73C7385D6}" name="5" dataDxfId="13"/>
-    <tableColumn id="15" xr3:uid="{AE2255F0-55BB-4EBA-B555-53C08E0AD340}" name="6" dataDxfId="12"/>
-    <tableColumn id="16" xr3:uid="{DC10F21C-EEC5-451A-8133-6C400CEFA48A}" name="7" dataDxfId="11"/>
-    <tableColumn id="17" xr3:uid="{5B0E20C0-A965-47E7-B220-2FC3781808A2}" name="8" dataDxfId="10"/>
-    <tableColumn id="18" xr3:uid="{9012B878-29D5-429E-AE2F-702FE0B7E4ED}" name="9" dataDxfId="9"/>
-    <tableColumn id="19" xr3:uid="{795A1C20-3F30-4D31-B2C1-616178E686C5}" name="10" dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{BD14ACEA-4C27-407B-9F44-4441FAE0A695}" name="11" dataDxfId="7"/>
-    <tableColumn id="21" xr3:uid="{559389C0-BFC6-48DE-827C-5706F746A67F}" name="12" dataDxfId="6"/>
-    <tableColumn id="22" xr3:uid="{22B66430-28FB-4EFF-86DA-E6FEF13427A1}" name="13" dataDxfId="5"/>
-    <tableColumn id="23" xr3:uid="{FD7803DF-E65A-4D87-A1DA-FDAA6B392D2B}" name="14" dataDxfId="4"/>
-    <tableColumn id="24" xr3:uid="{41BBF050-A9B4-49FF-A7B3-AF5D66D03162}" name="15" dataDxfId="3"/>
-    <tableColumn id="25" xr3:uid="{B2BFE9A6-F6A1-4867-B0FA-CC30A76A7754}" name="16" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{E07AB1DB-5D76-4D4A-ABBD-E5E9E50EB8C7}" name="0" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{81717C64-19AE-4844-B7F9-777899752382}" name="1" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{F74E9D07-6EA1-47BA-859A-8EC6358D2293}" name="2" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{072BA86D-F274-4183-96F9-728CC82922D9}" name="3" dataDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{E36BC491-A68B-4595-9F73-4EC8782C8890}" name="4" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{84AC78DB-F38E-4A09-B16E-6FC73C7385D6}" name="5" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{AE2255F0-55BB-4EBA-B555-53C08E0AD340}" name="6" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{DC10F21C-EEC5-451A-8133-6C400CEFA48A}" name="7" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{5B0E20C0-A965-47E7-B220-2FC3781808A2}" name="8" dataDxfId="8"/>
+    <tableColumn id="18" xr3:uid="{9012B878-29D5-429E-AE2F-702FE0B7E4ED}" name="9" dataDxfId="7"/>
+    <tableColumn id="19" xr3:uid="{795A1C20-3F30-4D31-B2C1-616178E686C5}" name="10" dataDxfId="6"/>
+    <tableColumn id="20" xr3:uid="{BD14ACEA-4C27-407B-9F44-4441FAE0A695}" name="11" dataDxfId="5"/>
+    <tableColumn id="21" xr3:uid="{559389C0-BFC6-48DE-827C-5706F746A67F}" name="12" dataDxfId="4"/>
+    <tableColumn id="22" xr3:uid="{22B66430-28FB-4EFF-86DA-E6FEF13427A1}" name="13" dataDxfId="3"/>
+    <tableColumn id="23" xr3:uid="{FD7803DF-E65A-4D87-A1DA-FDAA6B392D2B}" name="14" dataDxfId="2"/>
+    <tableColumn id="24" xr3:uid="{41BBF050-A9B4-49FF-A7B3-AF5D66D03162}" name="15" dataDxfId="1"/>
+    <tableColumn id="25" xr3:uid="{B2BFE9A6-F6A1-4867-B0FA-CC30A76A7754}" name="16" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1162,7 +1168,7 @@
         <v>22</v>
       </c>
       <c r="G2" s="6">
-        <f>SUM(I2:Z2)</f>
+        <f t="shared" ref="G2:G15" si="0">SUM(I2:Z2)</f>
         <v>24</v>
       </c>
       <c r="H2" s="4" t="str">
@@ -1197,91 +1203,79 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="5">
-        <f t="shared" ref="F3:F14" si="0">SUM(C3:E3)</f>
+    <row r="3" spans="1:25" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="9">
+        <f t="shared" ref="F3:F14" si="1">SUM(C3:E3)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="6">
-        <f>SUM(I3:Z3)</f>
-        <v>3</v>
-      </c>
-      <c r="H3" s="4" t="str">
-        <f t="shared" ref="H3:H15" si="1">IF(G3&gt;=F3, "OK", "")</f>
-        <v>OK</v>
-      </c>
-      <c r="M3" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="8">
-        <v>2</v>
-      </c>
-      <c r="F4" s="9">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G4" s="10">
-        <f>SUM(I4:Z4)</f>
-        <v>4</v>
-      </c>
-      <c r="H4" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>OK</v>
-      </c>
-      <c r="J4" s="8">
-        <v>1</v>
-      </c>
-      <c r="O4" s="8">
-        <v>1</v>
-      </c>
-      <c r="T4" s="8">
-        <v>1</v>
-      </c>
-      <c r="U4" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="G3" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G5" s="6">
-        <f>SUM(I5:Z5)</f>
+      <c r="H3" s="8" t="str">
+        <f t="shared" ref="H3:H15" si="2">IF(G3&gt;=F3, "OK", "")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="H5" s="4" t="str">
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4">
+        <v>2</v>
+      </c>
+      <c r="F4" s="5">
         <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="G4" s="6">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H4" s="4" t="str">
+        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
-      <c r="O5" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>2</v>
+      <c r="J4" s="4">
+        <v>1</v>
+      </c>
+      <c r="O4" s="4">
+        <v>1</v>
+      </c>
+      <c r="T4" s="4">
+        <v>1</v>
+      </c>
+      <c r="U4" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H5" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>OK</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
@@ -1298,15 +1292,15 @@
         <v>6</v>
       </c>
       <c r="F6" s="5">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="G6" s="6">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="G6" s="6">
-        <f>SUM(I6:Z6)</f>
         <v>14</v>
       </c>
       <c r="H6" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="I6" s="4">
@@ -1345,15 +1339,15 @@
         <v>12</v>
       </c>
       <c r="F7" s="5">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="G7" s="6">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="G7" s="6">
-        <f>SUM(I7:Z7)</f>
         <v>14</v>
       </c>
       <c r="H7" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="I7" s="4">
@@ -1389,15 +1383,15 @@
         <v>3</v>
       </c>
       <c r="F8" s="5">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="G8" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G8" s="6">
-        <f>SUM(I8:Z8)</f>
         <v>5</v>
       </c>
       <c r="H8" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="J8" s="4">
@@ -1430,15 +1424,15 @@
         <v>8</v>
       </c>
       <c r="F9" s="5">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="G9" s="6">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="G9" s="6">
-        <f>SUM(I9:Z9)</f>
         <v>18</v>
       </c>
       <c r="H9" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="I9" s="4">
@@ -1483,15 +1477,15 @@
         <v>3</v>
       </c>
       <c r="F10" s="5">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="G10" s="6">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="G10" s="6">
-        <f>SUM(I10:Z10)</f>
         <v>9</v>
       </c>
       <c r="H10" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="J10" s="4">
@@ -1527,15 +1521,15 @@
         <v>14</v>
       </c>
       <c r="F11" s="5">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="G11" s="6">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="G11" s="6">
-        <f>SUM(I11:Z11)</f>
         <v>16</v>
       </c>
       <c r="H11" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="K11" s="4">
@@ -1571,15 +1565,15 @@
         <v>15</v>
       </c>
       <c r="F12" s="5">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="G12" s="6">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="G12" s="6">
-        <f>SUM(I12:Z12)</f>
         <v>17</v>
       </c>
       <c r="H12" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="I12" s="4">
@@ -1615,15 +1609,15 @@
         <v>2</v>
       </c>
       <c r="F13" s="5">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="G13" s="6">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G13" s="6">
-        <f>SUM(I13:Z13)</f>
         <v>4</v>
       </c>
       <c r="H13" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="L13" s="4">
@@ -1647,15 +1641,15 @@
         <v>3</v>
       </c>
       <c r="F14" s="5">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="G14" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G14" s="6">
-        <f>SUM(I14:Z14)</f>
         <v>5</v>
       </c>
       <c r="H14" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="L14" s="4">
@@ -1668,27 +1662,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
+    <row r="15" spans="1:25" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="9">
         <f>SUM(C15:E15)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="6">
-        <f>SUM(I15:Z15)</f>
-        <v>2</v>
-      </c>
-      <c r="H15" s="4" t="str">
-        <f t="shared" si="1"/>
+      <c r="G15" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="8" t="str">
+        <f t="shared" si="2"/>
         <v>OK</v>
-      </c>
-      <c r="J15" s="4">
-        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">

--- a/Items.xlsx
+++ b/Items.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\3D Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\Unity\TheClaw\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C94A25-1802-42E1-87D1-FAEACF0984B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
